--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\_Working\BreezeWorks\GagWriter Remastered\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B8CD64-8B5E-46A4-9725-9D94164BA6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3360BB67-2782-4874-9CD4-301831A4BC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13425" yWindow="10680" windowWidth="28770" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13755" yWindow="285" windowWidth="29490" windowHeight="30945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="114">
   <si>
     <t>Central</t>
   </si>
@@ -200,9 +200,6 @@
     <t>2,</t>
   </si>
   <si>
-    <t>3,</t>
-  </si>
-  <si>
     <t>A) first</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>0,0</t>
+  </si>
+  <si>
+    <t>1,</t>
   </si>
 </sst>
 </file>
@@ -471,13 +471,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -797,13 +796,13 @@
   <sheetData>
     <row r="4" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
         <v>45</v>
       </c>
       <c r="Q4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S4" t="s">
         <v>42</v>
@@ -847,10 +846,10 @@
         <v>49</v>
       </c>
       <c r="Y5" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" t="s">
         <v>73</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>74</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -891,13 +890,13 @@
     </row>
     <row r="6" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
         <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" t="s">
-        <v>99</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -994,13 +993,13 @@
     </row>
     <row r="7" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -1097,7 +1096,7 @@
     </row>
     <row r="8" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P8">
         <v>3</v>
@@ -1288,7 +1287,7 @@
     </row>
     <row r="10" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P10">
         <v>5</v>
@@ -1491,16 +1490,16 @@
     </row>
     <row r="12" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
         <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>99</v>
       </c>
       <c r="P12">
         <v>7</v>
@@ -1597,13 +1596,13 @@
     </row>
     <row r="13" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P13">
         <v>8</v>
@@ -1700,7 +1699,7 @@
     </row>
     <row r="14" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P14">
         <v>9</v>
@@ -1785,7 +1784,7 @@
     </row>
     <row r="15" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S15">
         <v>1</v>
@@ -1876,7 +1875,7 @@
     </row>
     <row r="16" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S16">
         <v>1</v>
@@ -2237,7 +2236,7 @@
         <v>13</v>
       </c>
       <c r="J20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S20">
         <v>2</v>
@@ -2331,7 +2330,7 @@
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J21" t="s">
         <v>37</v>
@@ -2428,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s">
         <v>38</v>
@@ -2703,7 +2702,7 @@
       <c r="C25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="4"/>
@@ -2812,17 +2811,17 @@
       <c r="C26" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="6">
-        <v>22</v>
+      <c r="D26" s="5">
+        <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J26" t="s">
         <v>4</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S26">
         <v>2</v>
@@ -2916,19 +2915,19 @@
         <v>6</v>
       </c>
       <c r="D27" s="1">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
         <v>3</v>
@@ -3022,19 +3021,19 @@
         <v>18</v>
       </c>
       <c r="D28" s="1">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
         <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J28" t="s">
         <v>21</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S28">
         <v>3</v>
@@ -3128,16 +3127,16 @@
         <v>16</v>
       </c>
       <c r="D29" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J29" t="s">
         <v>35</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S29">
         <v>3</v>
@@ -3231,19 +3230,19 @@
         <v>17</v>
       </c>
       <c r="D30" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>3</v>
@@ -3337,19 +3336,19 @@
         <v>3</v>
       </c>
       <c r="D31" s="1">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>3</v>
@@ -3446,19 +3445,19 @@
         <v>19</v>
       </c>
       <c r="D32" s="1">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S32">
         <v>3</v>
@@ -3552,19 +3551,19 @@
         <v>20</v>
       </c>
       <c r="D33" s="1">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S33">
         <v>3</v>
@@ -3661,19 +3660,19 @@
         <v>5</v>
       </c>
       <c r="D34" s="1">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" t="s">
         <v>5</v>
       </c>
       <c r="K34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S34">
         <v>4</v>
@@ -3767,19 +3766,19 @@
         <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J35" t="s">
         <v>33</v>
       </c>
       <c r="K35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S35">
         <v>4</v>
@@ -3873,19 +3872,19 @@
         <v>21</v>
       </c>
       <c r="D36" s="1">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J36" t="s">
         <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S36">
         <v>4</v>
@@ -3979,16 +3978,16 @@
         <v>22</v>
       </c>
       <c r="D37" s="1">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S37">
         <v>4</v>
@@ -4085,13 +4084,13 @@
         <v>23</v>
       </c>
       <c r="D38" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>4</v>
@@ -4185,16 +4184,16 @@
         <v>24</v>
       </c>
       <c r="D39" s="1">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S39">
         <v>4</v>
@@ -4291,13 +4290,13 @@
         <v>4</v>
       </c>
       <c r="D40" s="1">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -4394,13 +4393,13 @@
         <v>25</v>
       </c>
       <c r="D41" s="1">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -4496,14 +4495,14 @@
       <c r="C42" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="1">
-        <v>14</v>
+      <c r="D42" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="F42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J42">
         <v>3</v>
@@ -4599,14 +4598,14 @@
       <c r="C43" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="1">
-        <v>12</v>
+      <c r="D43" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
         <v>4</v>
@@ -4702,14 +4701,14 @@
       <c r="C44" t="s">
         <v>2</v>
       </c>
-      <c r="D44" s="1">
-        <v>15</v>
+      <c r="D44" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -4806,7 +4805,7 @@
         <v>28</v>
       </c>
       <c r="D45" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="S45">
         <v>5</v>
@@ -4903,7 +4902,7 @@
         <v>29</v>
       </c>
       <c r="D46" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="S46">
         <v>5</v>
@@ -4997,7 +4996,7 @@
         <v>30</v>
       </c>
       <c r="D47" s="1">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="S47">
         <v>5</v>
@@ -5094,7 +5093,7 @@
         <v>31</v>
       </c>
       <c r="D48" s="1">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="S48">
         <v>6</v>
@@ -5188,7 +5187,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="1">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="S49">
         <v>6</v>
@@ -5282,7 +5281,7 @@
         <v>33</v>
       </c>
       <c r="D50" s="1">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="S50">
         <v>6</v>
@@ -5375,8 +5374,8 @@
       <c r="C51" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="1">
-        <v>13</v>
+      <c r="D51" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="S51">
         <v>6</v>
@@ -5562,7 +5561,7 @@
         <v>35</v>
       </c>
       <c r="D53" s="1">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="S53">
         <v>6</v>
@@ -5659,7 +5658,7 @@
         <v>36</v>
       </c>
       <c r="D54" s="1">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="S54">
         <v>6</v>
@@ -5753,7 +5752,7 @@
         <v>41</v>
       </c>
       <c r="D55" s="1">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="2:42" x14ac:dyDescent="0.25">
@@ -5761,7 +5760,7 @@
         <v>39</v>
       </c>
       <c r="D56" s="1">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="AB56" t="str">
         <f>_xlfn.TEXTJOIN(", ",TRUE, AB6:AB54)</f>
@@ -5820,21 +5819,21 @@
       <c r="C57" t="s">
         <v>40</v>
       </c>
-      <c r="D57" s="1">
-        <v>11</v>
+      <c r="D57" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60" t="str">
         <f>_xlfn.TEXTJOIN(", ", TRUE,AB56:AM56)</f>
@@ -5843,21 +5842,21 @@
     </row>
     <row r="64" spans="2:42" x14ac:dyDescent="0.25">
       <c r="K64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M64" t="s">
+        <v>91</v>
+      </c>
+      <c r="N64" t="s">
+        <v>106</v>
+      </c>
+      <c r="O64" t="s">
         <v>92</v>
-      </c>
-      <c r="N64" t="s">
-        <v>107</v>
-      </c>
-      <c r="O64" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="65" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -5871,7 +5870,7 @@
     </row>
     <row r="66" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M66">
         <v>1</v>
@@ -5885,7 +5884,7 @@
     </row>
     <row r="67" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M67">
         <v>2</v>
@@ -5899,7 +5898,7 @@
     </row>
     <row r="68" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M68">
         <v>3</v>
@@ -5913,7 +5912,7 @@
     </row>
     <row r="69" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M69">
         <v>4</v>
@@ -5927,7 +5926,7 @@
     </row>
     <row r="70" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M70">
         <v>5</v>
@@ -5941,7 +5940,7 @@
     </row>
     <row r="71" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M71">
         <v>6</v>
@@ -5955,7 +5954,7 @@
     </row>
     <row r="73" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O73" t="s">
         <v>25</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\_Working\BreezeWorks\GagWriter Remastered\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3360BB67-2782-4874-9CD4-301831A4BC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C252B9-C23B-4586-A64D-A6BABCCFCD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13755" yWindow="285" windowWidth="29490" windowHeight="30945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57495" yWindow="8025" windowWidth="19905" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
   <si>
     <t>Central</t>
   </si>
@@ -378,6 +378,48 @@
   </si>
   <si>
     <t>1,</t>
+  </si>
+  <si>
+    <t>simultaneous image/sound</t>
+  </si>
+  <si>
+    <t>5,</t>
+  </si>
+  <si>
+    <t>gpio expander</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>sig reserved</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>0,6 I guess</t>
   </si>
 </sst>
 </file>
@@ -775,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:AP73"/>
+  <dimension ref="B4:AP76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
@@ -3130,7 +3172,10 @@
         <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>114</v>
+      </c>
+      <c r="G29" t="s">
+        <v>115</v>
       </c>
       <c r="J29" t="s">
         <v>35</v>
@@ -3233,10 +3278,7 @@
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J30" t="s">
         <v>93</v>
@@ -3339,10 +3381,10 @@
         <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="s">
         <v>94</v>
@@ -3448,10 +3490,10 @@
         <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="s">
         <v>74</v>
@@ -3554,10 +3596,10 @@
         <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
@@ -3663,10 +3705,10 @@
         <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34" t="s">
         <v>5</v>
@@ -3769,10 +3811,10 @@
         <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" t="s">
         <v>33</v>
@@ -3875,10 +3917,10 @@
         <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" t="s">
         <v>25</v>
@@ -3981,7 +4023,10 @@
         <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -4087,10 +4132,7 @@
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="S38">
         <v>4</v>
@@ -4187,13 +4229,16 @@
         <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
         <v>95</v>
+      </c>
+      <c r="K39" t="s">
+        <v>127</v>
       </c>
       <c r="S39">
         <v>4</v>
@@ -4293,10 +4338,10 @@
         <v>42</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -4396,10 +4441,10 @@
         <v>43</v>
       </c>
       <c r="F41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -4499,10 +4544,10 @@
         <v>111</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J42">
         <v>3</v>
@@ -4602,10 +4647,10 @@
         <v>109</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43">
         <v>4</v>
@@ -4705,10 +4750,10 @@
         <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -4806,6 +4851,12 @@
       </c>
       <c r="D45" s="1">
         <v>15</v>
+      </c>
+      <c r="F45" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45">
+        <v>6</v>
       </c>
       <c r="S45">
         <v>5</v>
@@ -5853,8 +5904,11 @@
       <c r="O64" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="65" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q64" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K65" t="s">
         <v>83</v>
       </c>
@@ -5867,8 +5921,11 @@
       <c r="O65" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="66" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q65" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K66" t="s">
         <v>84</v>
       </c>
@@ -5881,8 +5938,11 @@
       <c r="O66" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="67" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q66" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K67" t="s">
         <v>85</v>
       </c>
@@ -5895,8 +5955,11 @@
       <c r="O67" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="68" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q67" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K68" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +5972,11 @@
       <c r="O68" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="69" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q68" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K69" t="s">
         <v>87</v>
       </c>
@@ -5923,8 +5989,11 @@
       <c r="O69" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="70" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q69" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="70" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K70" t="s">
         <v>88</v>
       </c>
@@ -5937,8 +6006,11 @@
       <c r="O70" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q70" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K71" t="s">
         <v>89</v>
       </c>
@@ -5951,13 +6023,27 @@
       <c r="O71" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="73" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="Q71" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K73" t="s">
         <v>96</v>
       </c>
       <c r="O73" t="s">
         <v>25</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K76" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
